--- a/Documentation/Developments.xlsx
+++ b/Documentation/Developments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca212f0ddc91cf85/Documents/Business/BurdySetUp/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{A8868D6A-38B5-42EC-9E3F-2EEA1017C54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0A2CE39-0B5D-4CF9-9BE5-00D27EF07554}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{A8868D6A-38B5-42EC-9E3F-2EEA1017C54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A08F6EC3-C81E-41EE-8609-CEE5B5071DA5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{92A20344-BE99-42D6-8702-E5B8A1301A57}"/>
   </bookViews>
@@ -1384,7 +1384,7 @@
       <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D7" t="s">
